--- a/ig/nriss-patch-1/CodeSystem-competence-code-system.xlsx
+++ b/ig/nriss-patch-1/CodeSystem-competence-code-system.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:45:21+00:00</t>
+    <t>2023-05-08T14:50:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nriss-patch-1/CodeSystem-competence-code-system.xlsx
+++ b/ig/nriss-patch-1/CodeSystem-competence-code-system.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:50:44+00:00</t>
+    <t>2023-05-08T14:52:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
